--- a/public/sap-reporting/expansion-150-downloads/EXT-MM19-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM19-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R31e53162dc9e429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rdd05bb7ed0874529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R9685e450ed784a63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R56dabe9e3d9d48ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R46755448abb448fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R797106b1b63d4979"/>
   </x:sheets>
 </x:workbook>
 </file>
